--- a/dev/mii-cm-pro-phq-9-linkid-migration.xlsx
+++ b/dev/mii-cm-pro-phq-9-linkid-migration.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.5.2</t>
+    <t>2026.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T21:31:58+00:00</t>
+    <t>2026-09-02T06:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/mii-cm-pro-phq-9-linkid-migration.xlsx
+++ b/dev/mii-cm-pro-phq-9-linkid-migration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="51">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.6.0</t>
+    <t>2026.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:53+00:00</t>
+    <t>2026-09-02T06:41:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,16 +93,13 @@
     <t>Source</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-pro/Questionnaire/mii-qst-pro-phq-9</t>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Relationship</t>
   </si>
   <si>
     <t>Target</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Relationship</t>
   </si>
   <si>
     <t/>
@@ -302,7 +299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -414,22 +411,6 @@
         <v>24</v>
       </c>
       <c r="B14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>26</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -446,158 +427,158 @@
         <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="C1" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>27</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2"/>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>33</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2"/>
     </row>

--- a/dev/mii-cm-pro-phq-9-linkid-migration.xlsx
+++ b/dev/mii-cm-pro-phq-9-linkid-migration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:55+00:00</t>
+    <t>2026-09-02T06:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>Target</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-pro/Questionnaire/mii-qst-pro-phq-9</t>
   </si>
   <si>
     <t/>
@@ -440,145 +443,149 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2"/>
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
       <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="C2" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="D2" s="2"/>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2"/>
     </row>

--- a/dev/mii-cm-pro-phq-9-linkid-migration.xlsx
+++ b/dev/mii-cm-pro-phq-9-linkid-migration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:47:03+00:00</t>
+    <t>2026-09-02T07:20:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
